--- a/etf_holdings/2026-10-08_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.89%920,000</t>
+          <t>14.40%920,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.89%</t>
+          <t>14.40%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.58%1705</t>
+          <t>-1.17%1685</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1705</v>
+        <v>1685</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.01%373,000</t>
+          <t>3.10%300,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>373000</v>
+        <v>300000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.82%365.5</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>365.5</v>
+        <v>3440</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.49%1,467,000</t>
+          <t>3.07%143,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1467000</v>
+        <v>143000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3545</v>
+        <v>7165</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.05%132,000</t>
+          <t>2.97%72,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>132000</v>
+        <v>72000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5950</v>
+        <v>1270</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.00%80,000</t>
+          <t>2.94%372,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>80000</v>
+        <v>372000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2015</v>
+        <v>6000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.98%232,000</t>
+          <t>2.88%80,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>232000</v>
+        <v>80000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>732</v>
+        <v>2070</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.82%605,000</t>
+          <t>2.83%232,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>605000</v>
+        <v>232000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.68%733</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>733</v>
+        <v>10615</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.76%598,000</t>
+          <t>2.78%39,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>598000</v>
+        <v>39000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,25 +992,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>0%106</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>647</v>
+        <v>106</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.72%694,000</t>
+          <t>2.72%4,243,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>694000</v>
+        <v>4243000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.44%106</t>
+          <t>-0.68%363</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>106</v>
+        <v>363</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.57%3,926,000</t>
+          <t>2.60%1,175,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3926000</v>
+        <v>1175000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3140</v>
+        <v>147.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.49%136,000</t>
+          <t>2.41%2,684,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>136000</v>
+        <v>2684000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>-1.85%635</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6805</v>
+        <v>635</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.48%56,000</t>
+          <t>2.39%609,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>56000</v>
+        <v>609000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11790</v>
+        <v>744</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.30%28,000</t>
+          <t>2.19%493,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>28000</v>
+        <v>493000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>+0.68%5925</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1305</v>
+        <v>5925</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.20%268,000</t>
+          <t>2.17%61,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>268000</v>
+        <v>61000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:40</t>
+          <t>2026-10-08 23:53:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.31%1000</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.31%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>6660</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.20%336,000</t>
+          <t>2.07%50,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>336000</v>
+        <v>50000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-2%980</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6845</v>
+        <v>980</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.15%50,000</t>
+          <t>2.03%336,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>50000</v>
+        <v>336000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>+0.13%75.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4835</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.06%67,000</t>
+          <t>2.01%4,400,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>67000</v>
+        <v>4400000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>148.5</v>
+        <v>2960</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.02%2,186,000</t>
+          <t>1.94%102,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2186000</v>
+        <v>102000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.34%5885</t>
+          <t>-0.82%727</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5885</v>
+        <v>727</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.00%54,000</t>
+          <t>1.80%406,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>54000</v>
+        <v>406000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0%145.5</t>
+          <t>0%215.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1677,20 +1677,20 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>145.5</v>
+        <v>215.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.72%1,888,000</t>
+          <t>1.70%1,304,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1888000</v>
+        <v>1304000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2240</v>
+        <v>2360</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.64%114,036</t>
+          <t>1.70%121,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>114036</v>
+        <v>121000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%1535</t>
+          <t>+0.69%146.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1535</v>
+        <v>146.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.58%164,000</t>
+          <t>1.66%1,888,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>164000</v>
+        <v>1888000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1990</v>
+        <v>2240</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.54%120,000</t>
+          <t>1.55%114,036</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>120000</v>
+        <v>114036</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>1605華新</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.44%75.5</t>
+          <t>-2.01%39.1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>75.5</v>
+        <v>39.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.51%3,264,000</t>
+          <t>1.54%6,362,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3264000</v>
+        <v>6362000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>1101台泥</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>+0.78%25.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2315</v>
+        <v>25.7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.51%104,000</t>
+          <t>1.52%9,821,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>104000</v>
+        <v>9821000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.56%252</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>252</v>
+        <v>1525</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.46%910,000</t>
+          <t>1.52%164,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>910000</v>
+        <v>164000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.83%1215</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1215</v>
+        <v>4690</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.41%187,000</t>
+          <t>1.46%50,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>187000</v>
+        <v>50000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+10%1815</t>
+          <t>-0.98%20.15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1815</v>
+        <v>20.15</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.39%135,000</t>
+          <t>1.41%11,436,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>135000</v>
+        <v>11436000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.68%588</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>588</v>
+        <v>249</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.32%357,000</t>
+          <t>1.39%910,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>357000</v>
+        <v>910000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:41</t>
+          <t>2026-10-08 23:53:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>+3.7%4345</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1100</v>
+        <v>4345</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.27%189,000</t>
+          <t>1.29%51,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>189000</v>
+        <v>51000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1480</v>
+        <v>1075</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.21%128,000</t>
+          <t>1.26%189,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>128000</v>
+        <v>189000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.76%1995</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1995</v>
+        <v>1965</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.20%97,000</t>
+          <t>1.25%104,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>97000</v>
+        <v>104000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.69%232.5</t>
+          <t>-7%1130</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>232.5</v>
+        <v>1130</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.17%787,000</t>
+          <t>1.23%167,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>787000</v>
+        <v>167000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.24%20.35</t>
+          <t>-0.83%1195</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>20.35</v>
+        <v>1195</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.11%8,783,000</t>
+          <t>1.22%167,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>8783000</v>
+        <v>167000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>-1%1975</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>514</v>
+        <v>1975</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.02%310,000</t>
+          <t>1.17%97,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>310000</v>
+        <v>97000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+2.55%1205</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1205</v>
+        <v>1475</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.02%138,000</t>
+          <t>1.15%128,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>138000</v>
+        <v>128000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>0%232.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1245</v>
+        <v>232.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.99%126,000</t>
+          <t>1.11%787,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>126000</v>
+        <v>787000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1504東元</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.09%73.3</t>
+          <t>-1.19%581</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.09%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>73.3</v>
+        <v>581</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.97%2,177,000</t>
+          <t>0.99%278,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2177000</v>
+        <v>278000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1605華新</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.97%39.9</t>
+          <t>-1.65%1785</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>39.9</v>
+        <v>1785</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.88%3,636,000</t>
+          <t>0.99%90,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>3636000</v>
+        <v>90000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1101台泥</t>
+          <t>1504東元</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.19%25.5</t>
+          <t>-2.18%71.7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>25.5</v>
+        <v>71.7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.77%4,878,000</t>
+          <t>0.97%2,177,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>4878000</v>
+        <v>2177000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.24%4190</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4190</v>
+        <v>532</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.76%29,000</t>
+          <t>0.96%310,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>29000</v>
+        <v>310000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+9.91%75.4</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>75.40000000000001</v>
+        <v>1285</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.68%1,589,000</t>
+          <t>0.95%126,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1589000</v>
+        <v>126000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.1%47.75</t>
+          <t>+7.82%81.3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+7.82%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>47.75</v>
+        <v>81.3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.63%2,097,000</t>
+          <t>0.73%1,589,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2097000</v>
+        <v>1589000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+1.05%48.25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1645</v>
+        <v>48.25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.55%55,000</t>
+          <t>0.61%2,097,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>55000</v>
+        <v>2097000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:43</t>
+          <t>2026-10-08 23:53:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-6.65%786</t>
+          <t>+1.91%801</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.65%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.54%102,000</t>
+          <t>0.49%102,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:44</t>
+          <t>2026-10-08 23:53:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.65%156</t>
+          <t>-0.96%154.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>156</v>
+        <v>154.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.50%511,000</t>
+          <t>0.48%511,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:44</t>
+          <t>2026-10-08 23:53:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.13%179.5</t>
+          <t>-1.39%177</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.27%243,000</t>
+          <t>0.26%243,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:44</t>
+          <t>2026-10-08 23:53:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+6.93%231.5</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+6.93%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>231.5</v>
+        <v>1710</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.19%141,000</t>
+          <t>0.20%20,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>141000</v>
+        <v>20000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:44</t>
+          <t>2026-10-08 23:53:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.33%1525</t>
+          <t>-0.33%1520</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:44</t>
+          <t>2026-10-08 23:53:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.65%155.5</t>
+          <t>-1.61%153</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>155.5</v>
+        <v>153</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
